--- a/event_registration_forms/021_event_stage_design_feedback_questionnaire--event_registration_forms.xlsx
+++ b/event_registration_forms/021_event_stage_design_feedback_questionnaire--event_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -730,12 +730,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="32" customWidth="1" min="2" max="2"/>
-    <col width="32" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -763,12 +763,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -780,12 +780,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -797,12 +797,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -814,12 +814,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'somewhat_satisfied'}</t>
+          <t>satisfied</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Somewhat Satisfied'}</t>
+          <t>Satisfied</t>
         </is>
       </c>
     </row>
@@ -831,29 +831,29 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>event_stage_designer_choices</t>
+          <t>event_stager_choices</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'very_satisfied'}</t>
+          <t>not_available</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Very Satisfied'}</t>
+          <t>Not Available</t>
         </is>
       </c>
     </row>
@@ -865,12 +865,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'not_available'}</t>
+          <t>present</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Not Available'}</t>
+          <t>Present</t>
         </is>
       </c>
     </row>
@@ -882,29 +882,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'present'}</t>
+          <t>absent</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Present'}</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>event_stager_choices</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>{'name':_'absent'}</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>{'name': 'Absent'}</t>
+          <t>Absent</t>
         </is>
       </c>
     </row>
